--- a/data/trans_orig/IP11A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11A-Edad-trans_orig.xlsx
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>462</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>68,11%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -4626,47 +4626,47 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>5179</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4930,49 +4930,49 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t>15066</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>42,67%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>15188</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>43,02%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>9944</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>21,37%</t>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -7091,12 +7091,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -7999,12 +7999,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9476,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>61194</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>35053</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>823</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -11750,12 +11750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -11863,12 +11863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11913,12 +11913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11948,12 +11948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12482,12 +12482,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -12545,12 +12545,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12560,12 +12560,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -12658,12 +12658,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -13041,7 +13041,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13312,12 +13312,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -13340,12 +13340,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13355,12 +13355,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13375,12 +13375,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13390,12 +13390,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13453,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13468,12 +13468,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -13566,12 +13566,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -13601,12 +13601,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13636,12 +13636,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14150,12 +14150,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14205,12 +14205,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14220,12 +14220,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -14248,12 +14248,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14263,12 +14263,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14361,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14396,12 +14396,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14411,12 +14411,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14509,12 +14509,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14524,12 +14524,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14544,12 +14544,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14559,12 +14559,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -14587,12 +14587,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14672,12 +14672,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -16705,12 +16705,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -17096,7 +17096,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17274,12 +17274,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17289,12 +17289,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17352,12 +17352,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>521</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -17367,12 +17367,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17387,12 +17387,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -17402,12 +17402,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -17430,12 +17430,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17465,12 +17465,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17480,12 +17480,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17500,12 +17500,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17515,12 +17515,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18197,12 +18197,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -18225,12 +18225,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18260,12 +18260,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18275,12 +18275,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18295,12 +18295,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18310,12 +18310,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -18338,12 +18338,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -18353,12 +18353,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -18408,12 +18408,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -18423,12 +18423,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -18977,12 +18977,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -18992,12 +18992,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -19020,12 +19020,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19055,12 +19055,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19070,12 +19070,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19105,12 +19105,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -19133,12 +19133,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19148,12 +19148,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19168,12 +19168,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19183,12 +19183,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19203,12 +19203,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19218,12 +19218,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -19246,12 +19246,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19261,12 +19261,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19331,12 +19331,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19394,12 +19394,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19409,12 +19409,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19429,12 +19429,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19444,12 +19444,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
